--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-research-study-category-vs.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-research-study-category-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:00:57+00:00</t>
+    <t>2026-09-11T09:17:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-research-study-category-vs.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-research-study-category-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T09:17:55+00:00</t>
+    <t>2026-09-11T09:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-research-study-category-vs.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-research-study-category-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T09:44:10+00:00</t>
+    <t>2026-09-11T09:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-research-study-category-vs.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-research-study-category-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T09:51:30+00:00</t>
+    <t>2026-01-09</t>
   </si>
   <si>
     <t>Publisher</t>
